--- a/ig/homecareobservation/StructureDefinition-medcom-homecareobservation-diagnosticreport.xlsx
+++ b/ig/homecareobservation/StructureDefinition-medcom-homecareobservation-diagnosticreport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.1</t>
+    <t>1.2.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-19T07:53:40+00:00</t>
+    <t>2026-06-03T08:12:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2746,7 +2746,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="11" hidden="true">
+    <row r="11">
       <c r="A11" t="s" s="2">
         <v>142</v>
       </c>
@@ -3892,7 +3892,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
         <v>219</v>
       </c>
@@ -4118,7 +4118,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
         <v>241</v>
       </c>
@@ -4228,7 +4228,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
         <v>250</v>
       </c>
@@ -4574,7 +4574,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
         <v>282</v>
       </c>
@@ -4806,7 +4806,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
         <v>306</v>
       </c>
@@ -4924,7 +4924,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
         <v>310</v>
       </c>
@@ -5274,7 +5274,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
         <v>329</v>
       </c>
@@ -5504,7 +5504,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
         <v>344</v>
       </c>
@@ -6076,7 +6076,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
         <v>364</v>
       </c>
@@ -6188,7 +6188,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="41" hidden="true">
+    <row r="41">
       <c r="A41" t="s" s="2">
         <v>369</v>
       </c>
@@ -6532,12 +6532,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AN43">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
